--- a/VerveStacks_ESP/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ESP/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C2A078E-47F9-44C9-926B-F6EDFE41976B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F28BC14F-EA47-43D9-9328-5A768A673252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7626,7 +7626,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E245BE3D-6058-4576-97CD-F19635DB0152}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D047537-3E05-45B4-8EAF-D52E70C3ACC8}">
   <dimension ref="B9:N58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9506,7 +9506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF14526-F5B8-432E-8B35-35B750709645}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2434490-698A-43CD-8975-0670D47B1251}">
   <dimension ref="B9:AB156"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20084,7 +20084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F813168-9FAC-46A2-90D4-00FCDD5454FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDB2BB2-CBDF-4AD5-B33E-27854AD6A06B}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ESP/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ESP/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F28BC14F-EA47-43D9-9328-5A768A673252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6261961-5D39-4966-B650-2F788305A7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7626,7 +7626,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D047537-3E05-45B4-8EAF-D52E70C3ACC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840FFA64-CBCA-42FA-98CC-3F9914C451D4}">
   <dimension ref="B9:N58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9506,7 +9506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2434490-698A-43CD-8975-0670D47B1251}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDD7DCF-6EC3-4080-886A-E5CF5B1CB974}">
   <dimension ref="B9:AB156"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20084,7 +20084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDB2BB2-CBDF-4AD5-B33E-27854AD6A06B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AB6527-F0BC-463D-B1A6-9E7C5DF78235}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ESP/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ESP/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ESP\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A8BF69C-6CBD-4DEA-AB4F-6AAB7683932F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1EB748-C6A9-4250-B1CC-DD21C8B90497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="411">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -618,6 +618,9 @@
     <t>wnid offshore potential</t>
   </si>
   <si>
+    <t>ELC_BatIn</t>
+  </si>
+  <si>
     <t>~fi_process</t>
   </si>
   <si>
@@ -645,7 +648,7 @@
     <t>ele</t>
   </si>
   <si>
-    <t>e_spv_001</t>
+    <t>e_spv_ESP_001</t>
   </si>
   <si>
     <t>solar resource in cluster 1</t>
@@ -657,151 +660,151 @@
     <t>no</t>
   </si>
   <si>
-    <t>e_spv_002</t>
+    <t>e_spv_ESP_002</t>
   </si>
   <si>
     <t>solar resource in cluster 2</t>
   </si>
   <si>
-    <t>e_spv_003</t>
+    <t>e_spv_ESP_003</t>
   </si>
   <si>
     <t>solar resource in cluster 3</t>
   </si>
   <si>
-    <t>e_spv_004</t>
+    <t>e_spv_ESP_004</t>
   </si>
   <si>
     <t>solar resource in cluster 4</t>
   </si>
   <si>
-    <t>e_spv_005</t>
+    <t>e_spv_ESP_005</t>
   </si>
   <si>
     <t>solar resource in cluster 5</t>
   </si>
   <si>
-    <t>e_spv_006</t>
+    <t>e_spv_ESP_006</t>
   </si>
   <si>
     <t>solar resource in cluster 6</t>
   </si>
   <si>
-    <t>e_spv_007</t>
+    <t>e_spv_ESP_007</t>
   </si>
   <si>
     <t>solar resource in cluster 7</t>
   </si>
   <si>
-    <t>e_spv_008</t>
+    <t>e_spv_ESP_008</t>
   </si>
   <si>
     <t>solar resource in cluster 8</t>
   </si>
   <si>
-    <t>e_spv_009</t>
+    <t>e_spv_ESP_009</t>
   </si>
   <si>
     <t>solar resource in cluster 9</t>
   </si>
   <si>
-    <t>e_spv_010</t>
+    <t>e_spv_ESP_010</t>
   </si>
   <si>
     <t>solar resource in cluster 10</t>
   </si>
   <si>
-    <t>e_spv_011</t>
+    <t>e_spv_ESP_011</t>
   </si>
   <si>
     <t>solar resource in cluster 11</t>
   </si>
   <si>
-    <t>e_spv_012</t>
+    <t>e_spv_ESP_012</t>
   </si>
   <si>
     <t>solar resource in cluster 12</t>
   </si>
   <si>
-    <t>e_spv_013</t>
+    <t>e_spv_ESP_013</t>
   </si>
   <si>
     <t>solar resource in cluster 13</t>
   </si>
   <si>
-    <t>e_spv_014</t>
+    <t>e_spv_ESP_014</t>
   </si>
   <si>
     <t>solar resource in cluster 14</t>
   </si>
   <si>
-    <t>e_spv_015</t>
+    <t>e_spv_ESP_015</t>
   </si>
   <si>
     <t>solar resource in cluster 15</t>
   </si>
   <si>
-    <t>e_spv_016</t>
+    <t>e_spv_ESP_016</t>
   </si>
   <si>
     <t>solar resource in cluster 16</t>
   </si>
   <si>
-    <t>e_spv_017</t>
+    <t>e_spv_ESP_017</t>
   </si>
   <si>
     <t>solar resource in cluster 17</t>
   </si>
   <si>
-    <t>e_spv_018</t>
+    <t>e_spv_ESP_018</t>
   </si>
   <si>
     <t>solar resource in cluster 18</t>
   </si>
   <si>
-    <t>e_spv_019</t>
+    <t>e_spv_ESP_019</t>
   </si>
   <si>
     <t>solar resource in cluster 19</t>
   </si>
   <si>
-    <t>e_spv_020</t>
+    <t>e_spv_ESP_020</t>
   </si>
   <si>
     <t>solar resource in cluster 20</t>
   </si>
   <si>
-    <t>e_spv_021</t>
+    <t>e_spv_ESP_021</t>
   </si>
   <si>
     <t>solar resource in cluster 21</t>
   </si>
   <si>
-    <t>e_spv_022</t>
+    <t>e_spv_ESP_022</t>
   </si>
   <si>
     <t>solar resource in cluster 22</t>
   </si>
   <si>
-    <t>e_spv_023</t>
+    <t>e_spv_ESP_023</t>
   </si>
   <si>
     <t>solar resource in cluster 23</t>
   </si>
   <si>
-    <t>e_spv_024</t>
+    <t>e_spv_ESP_024</t>
   </si>
   <si>
     <t>solar resource in cluster 24</t>
   </si>
   <si>
-    <t>e_spv_025</t>
+    <t>e_spv_ESP_025</t>
   </si>
   <si>
     <t>solar resource in cluster 25</t>
   </si>
   <si>
-    <t>e_spv_026</t>
+    <t>e_spv_ESP_026</t>
   </si>
   <si>
     <t>solar resource in cluster 26</t>
@@ -819,469 +822,469 @@
     <t>af~fx</t>
   </si>
   <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_011</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_014</t>
-  </si>
-  <si>
-    <t>elc_spv_015</t>
-  </si>
-  <si>
-    <t>elc_spv_016</t>
-  </si>
-  <si>
-    <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_019</t>
-  </si>
-  <si>
-    <t>elc_spv_020</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_022</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
-    <t>e_won_001</t>
+    <t>elc_spv_ESP_001</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_002</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_003</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_004</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_005</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_006</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_007</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_008</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_009</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_010</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_011</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_012</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_013</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_014</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_015</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_016</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_017</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_018</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_019</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_020</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_021</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_022</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_023</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_024</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_025</t>
+  </si>
+  <si>
+    <t>elc_spv_ESP_026</t>
+  </si>
+  <si>
+    <t>e_won_ESP_001</t>
   </si>
   <si>
     <t>wind resource in cluster 1</t>
   </si>
   <si>
-    <t>e_won_002</t>
+    <t>e_won_ESP_002</t>
   </si>
   <si>
     <t>wind resource in cluster 2</t>
   </si>
   <si>
-    <t>e_won_003</t>
+    <t>e_won_ESP_003</t>
   </si>
   <si>
     <t>wind resource in cluster 3</t>
   </si>
   <si>
-    <t>e_won_004</t>
+    <t>e_won_ESP_004</t>
   </si>
   <si>
     <t>wind resource in cluster 4</t>
   </si>
   <si>
-    <t>e_won_005</t>
+    <t>e_won_ESP_005</t>
   </si>
   <si>
     <t>wind resource in cluster 5</t>
   </si>
   <si>
-    <t>e_won_006</t>
+    <t>e_won_ESP_006</t>
   </si>
   <si>
     <t>wind resource in cluster 6</t>
   </si>
   <si>
-    <t>e_won_007</t>
+    <t>e_won_ESP_007</t>
   </si>
   <si>
     <t>wind resource in cluster 7</t>
   </si>
   <si>
-    <t>e_won_008</t>
+    <t>e_won_ESP_008</t>
   </si>
   <si>
     <t>wind resource in cluster 8</t>
   </si>
   <si>
-    <t>e_won_009</t>
+    <t>e_won_ESP_009</t>
   </si>
   <si>
     <t>wind resource in cluster 9</t>
   </si>
   <si>
-    <t>e_won_010</t>
+    <t>e_won_ESP_010</t>
   </si>
   <si>
     <t>wind resource in cluster 10</t>
   </si>
   <si>
-    <t>e_won_011</t>
+    <t>e_won_ESP_011</t>
   </si>
   <si>
     <t>wind resource in cluster 11</t>
   </si>
   <si>
-    <t>e_won_012</t>
+    <t>e_won_ESP_012</t>
   </si>
   <si>
     <t>wind resource in cluster 12</t>
   </si>
   <si>
-    <t>e_won_013</t>
+    <t>e_won_ESP_013</t>
   </si>
   <si>
     <t>wind resource in cluster 13</t>
   </si>
   <si>
-    <t>e_won_014</t>
+    <t>e_won_ESP_014</t>
   </si>
   <si>
     <t>wind resource in cluster 14</t>
   </si>
   <si>
-    <t>e_won_015</t>
+    <t>e_won_ESP_015</t>
   </si>
   <si>
     <t>wind resource in cluster 15</t>
   </si>
   <si>
-    <t>e_won_016</t>
+    <t>e_won_ESP_016</t>
   </si>
   <si>
     <t>wind resource in cluster 16</t>
   </si>
   <si>
-    <t>e_won_017</t>
+    <t>e_won_ESP_017</t>
   </si>
   <si>
     <t>wind resource in cluster 17</t>
   </si>
   <si>
-    <t>e_won_018</t>
+    <t>e_won_ESP_018</t>
   </si>
   <si>
     <t>wind resource in cluster 18</t>
   </si>
   <si>
-    <t>e_won_019</t>
+    <t>e_won_ESP_019</t>
   </si>
   <si>
     <t>wind resource in cluster 19</t>
   </si>
   <si>
-    <t>e_won_020</t>
+    <t>e_won_ESP_020</t>
   </si>
   <si>
     <t>wind resource in cluster 20</t>
   </si>
   <si>
-    <t>e_won_021</t>
+    <t>e_won_ESP_021</t>
   </si>
   <si>
     <t>wind resource in cluster 21</t>
   </si>
   <si>
-    <t>e_won_022</t>
+    <t>e_won_ESP_022</t>
   </si>
   <si>
     <t>wind resource in cluster 22</t>
   </si>
   <si>
-    <t>e_won_023</t>
+    <t>e_won_ESP_023</t>
   </si>
   <si>
     <t>wind resource in cluster 23</t>
   </si>
   <si>
-    <t>e_won_024</t>
+    <t>e_won_ESP_024</t>
   </si>
   <si>
     <t>wind resource in cluster 24</t>
   </si>
   <si>
-    <t>e_won_025</t>
+    <t>e_won_ESP_025</t>
   </si>
   <si>
     <t>wind resource in cluster 25</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_wof_001</t>
+    <t>elc_won_ESP_001</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_002</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_003</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_004</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_005</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_006</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_007</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_008</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_009</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_010</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_011</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_012</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_013</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_014</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_015</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_016</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_017</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_018</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_019</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_020</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_021</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_022</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_023</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_024</t>
+  </si>
+  <si>
+    <t>elc_won_ESP_025</t>
+  </si>
+  <si>
+    <t>e_wof_ESP_001</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 1</t>
   </si>
   <si>
-    <t>e_wof_002</t>
+    <t>e_wof_ESP_002</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 2</t>
   </si>
   <si>
-    <t>e_wof_003</t>
+    <t>e_wof_ESP_003</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 3</t>
   </si>
   <si>
-    <t>e_wof_004</t>
+    <t>e_wof_ESP_004</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 4</t>
   </si>
   <si>
-    <t>e_wof_005</t>
+    <t>e_wof_ESP_005</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 5</t>
   </si>
   <si>
-    <t>e_wof_006</t>
+    <t>e_wof_ESP_006</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 6</t>
   </si>
   <si>
-    <t>e_wof_007</t>
+    <t>e_wof_ESP_007</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 7</t>
   </si>
   <si>
-    <t>e_wof_008</t>
+    <t>e_wof_ESP_008</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 8</t>
   </si>
   <si>
-    <t>e_wof_009</t>
+    <t>e_wof_ESP_009</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 9</t>
   </si>
   <si>
-    <t>e_wof_010</t>
+    <t>e_wof_ESP_010</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 10</t>
   </si>
   <si>
-    <t>e_wof_011</t>
+    <t>e_wof_ESP_011</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 11</t>
   </si>
   <si>
-    <t>e_wof_012</t>
+    <t>e_wof_ESP_012</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 12</t>
   </si>
   <si>
-    <t>e_wof_013</t>
+    <t>e_wof_ESP_013</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 13</t>
   </si>
   <si>
-    <t>e_wof_014</t>
+    <t>e_wof_ESP_014</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 14</t>
   </si>
   <si>
-    <t>e_wof_015</t>
+    <t>e_wof_ESP_015</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 15</t>
   </si>
   <si>
-    <t>e_wof_016</t>
+    <t>e_wof_ESP_016</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 16</t>
   </si>
   <si>
-    <t>e_wof_017</t>
+    <t>e_wof_ESP_017</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 17</t>
   </si>
   <si>
-    <t>e_wof_018</t>
+    <t>e_wof_ESP_018</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 18</t>
   </si>
   <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
+    <t>elc_wof_ESP_001</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_002</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_003</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_005</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_007</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_008</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_010</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_011</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_012</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_013</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_014</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_015</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_016</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_017</t>
+  </si>
+  <si>
+    <t>elc_wof_ESP_018</t>
   </si>
   <si>
     <t>comm-in</t>
@@ -1371,7 +1374,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1519,8 +1522,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1612,6 +1622,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1826,7 +1841,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1846,8 +1861,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2239,6 +2255,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2258,8 +2275,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -2295,6 +2313,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -2652,423 +2673,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -3076,32 +2770,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -3109,37 +2803,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -3151,120 +2845,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1000</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
+        <v>Trd_electricity export</v>
+      </c>
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>1000</v>
+      </c>
+      <c r="S28">
+        <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
         <v>19</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>1000</v>
-      </c>
-      <c r="S18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1000</v>
-      </c>
-      <c r="S19">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4741,9 +4770,8 @@
     <row r="8" spans="2:25" ht="17.649999999999999">
       <c r="B8" s="20"/>
       <c r="E8" s="26"/>
-      <c r="F8" t="str">
-        <f>C5</f>
-        <v>ELC</v>
+      <c r="F8" t="s">
+        <v>163</v>
       </c>
       <c r="G8" t="str">
         <f>E7</f>
@@ -4810,25 +4838,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -4874,7 +4902,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -4919,7 +4947,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -4961,7 +4989,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6066,62 +6094,62 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE763B36-342F-424D-B5D1-900CDBBBC36D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80330D8D-D569-4E3D-AB14-1439EF2AE469}">
   <dimension ref="B9:M36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:13">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10" t="s">
-        <v>170</v>
-      </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
       <c r="K10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6130,33 +6158,33 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L11">
-        <v>7.9337400955112924</v>
+        <v>3.7756789747364841</v>
       </c>
       <c r="M11">
-        <v>0.17853980203530381</v>
+        <v>0.1819740516972255</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -6165,33 +6193,33 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L12">
-        <v>17.926169026688672</v>
+        <v>4.0325611207748118</v>
       </c>
       <c r="M12">
-        <v>0.21843370054268019</v>
+        <v>0.1753218712861746</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6200,33 +6228,33 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L13">
-        <v>9.3369895375679199</v>
+        <v>17.871369026688672</v>
       </c>
       <c r="M13">
-        <v>0.21024953309459971</v>
+        <v>0.21842656281226239</v>
       </c>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -6235,33 +6263,33 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L14">
-        <v>5.6064886916295897</v>
+        <v>9.1421895375679192</v>
       </c>
       <c r="M14">
-        <v>0.1908745847968695</v>
+        <v>0.21024122216574101</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6270,33 +6298,33 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L15">
-        <v>2.2219728680020312</v>
+        <v>5.5988886916295897</v>
       </c>
       <c r="M15">
-        <v>0.2277521864151259</v>
+        <v>0.19086942827325709</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6305,33 +6333,33 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L16">
-        <v>4.9673144150700139</v>
+        <v>4.9564144150700136</v>
       </c>
       <c r="M16">
-        <v>0.20520445664628981</v>
+        <v>0.20520261997757611</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -6340,33 +6368,33 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L17">
-        <v>10.095518726325738</v>
+        <v>5.2648190957010383</v>
       </c>
       <c r="M17">
-        <v>0.22455712179268</v>
+        <v>0.22030348474001729</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6375,33 +6403,33 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L18">
-        <v>28.547911715870871</v>
+        <v>5.6744874046694296</v>
       </c>
       <c r="M18">
-        <v>0.22481983585117399</v>
+        <v>0.21698008398260041</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6410,33 +6438,33 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L19">
-        <v>7.9370557611033314</v>
+        <v>9.2515780311731195</v>
       </c>
       <c r="M19">
-        <v>0.22058030591090269</v>
+        <v>0.23075245948820189</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6445,33 +6473,33 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L20">
-        <v>9.4413780311731212</v>
+        <v>21.018529946110469</v>
       </c>
       <c r="M20">
-        <v>0.23073937231432931</v>
+        <v>0.22838768290835759</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6480,33 +6508,33 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L21">
-        <v>35.481905898055416</v>
+        <v>18.769143939003545</v>
       </c>
       <c r="M21">
-        <v>0.2301091466075344</v>
+        <v>0.2315669998218931</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -6515,33 +6543,33 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L22">
-        <v>16.577517205019102</v>
+        <v>29.344708416127919</v>
       </c>
       <c r="M22">
-        <v>0.2368281943333751</v>
+        <v>0.23339770934652121</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -6550,33 +6578,33 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L23">
-        <v>6.3482090269509026</v>
+        <v>27.121911715870873</v>
       </c>
       <c r="M23">
-        <v>0.24685643073378141</v>
+        <v>0.22477625432130119</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -6585,33 +6613,33 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L24">
-        <v>15.134000918360217</v>
+        <v>17.860418483640107</v>
       </c>
       <c r="M24">
-        <v>0.24722067397672109</v>
+        <v>0.240009657978068</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -6620,33 +6648,33 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K25" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L25">
-        <v>20.62437842831179</v>
+        <v>15.140717205019104</v>
       </c>
       <c r="M25">
-        <v>0.236464822328638</v>
+        <v>0.23655911638096891</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -6655,33 +6683,33 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L26">
-        <v>25.411922885104712</v>
+        <v>11.845718107991869</v>
       </c>
       <c r="M26">
-        <v>0.2329034811425984</v>
+        <v>0.24650462559812769</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -6690,33 +6718,33 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K27" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L27">
-        <v>23.467964130074531</v>
+        <v>19.271164130074528</v>
       </c>
       <c r="M27">
-        <v>0.24037854001586439</v>
+        <v>0.23995461989575551</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -6725,33 +6753,33 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L28">
-        <v>15.041775060327886</v>
+        <v>12.010130206389354</v>
       </c>
       <c r="M28">
-        <v>0.2454034236711721</v>
+        <v>0.2451597287782552</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -6760,33 +6788,33 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L29">
-        <v>35.11317623889849</v>
+        <v>34.785395563683956</v>
       </c>
       <c r="M29">
-        <v>0.2358438878956105</v>
+        <v>0.23484249938153889</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D30" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -6795,33 +6823,33 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L30">
-        <v>24.68125062113489</v>
+        <v>14.868331296349432</v>
       </c>
       <c r="M30">
-        <v>0.23355551556807699</v>
+        <v>0.23467974891353249</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -6830,33 +6858,33 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L31">
-        <v>17.787621640472075</v>
+        <v>16.930021640472077</v>
       </c>
       <c r="M31">
-        <v>0.2326195907467522</v>
+        <v>0.2325461678333606</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -6865,33 +6893,33 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L32">
-        <v>17.607622711782451</v>
+        <v>17.593622711782448</v>
       </c>
       <c r="M32">
-        <v>0.18956958046781619</v>
+        <v>0.189562201955395</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -6900,33 +6928,33 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L33">
-        <v>13.09086038890036</v>
+        <v>12.32486038890036</v>
       </c>
       <c r="M33">
-        <v>0.21878120716462759</v>
+        <v>0.2186920540817637</v>
       </c>
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -6935,33 +6963,33 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L34">
-        <v>27.154162467447765</v>
+        <v>25.691262467447761</v>
       </c>
       <c r="M34">
-        <v>0.2240971404034573</v>
+        <v>0.22412039010071</v>
       </c>
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -6970,33 +6998,33 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L35">
-        <v>15.462194698870832</v>
+        <v>14.750894698870832</v>
       </c>
       <c r="M35">
-        <v>0.21006765409239969</v>
+        <v>0.2101455175853621</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -7005,22 +7033,22 @@
         <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L36">
-        <v>5.2161720372186871</v>
+        <v>5.1634720372186855</v>
       </c>
       <c r="M36">
-        <v>0.19028169258873209</v>
+        <v>0.19032553084645421</v>
       </c>
     </row>
   </sheetData>
@@ -7029,101 +7057,101 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA72CF9-A991-4407-BD0B-40AEED2B2E4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD635A7-93D0-4EE8-960E-F3C992861658}">
   <dimension ref="B9:Z35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:26">
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="2:26">
       <c r="B10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K10" t="s">
+        <v>228</v>
+      </c>
+      <c r="L10" t="s">
+        <v>229</v>
+      </c>
+      <c r="M10" t="s">
+        <v>230</v>
+      </c>
+      <c r="O10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="P10" t="s">
         <v>166</v>
       </c>
-      <c r="E10" t="s">
+      <c r="Q10" t="s">
         <v>167</v>
       </c>
-      <c r="F10" t="s">
+      <c r="R10" t="s">
         <v>168</v>
       </c>
-      <c r="G10" t="s">
+      <c r="S10" t="s">
         <v>169</v>
       </c>
-      <c r="H10" t="s">
+      <c r="T10" t="s">
         <v>170</v>
       </c>
-      <c r="J10" t="s">
-        <v>165</v>
-      </c>
-      <c r="K10" t="s">
-        <v>227</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="U10" t="s">
+        <v>171</v>
+      </c>
+      <c r="W10" t="s">
+        <v>166</v>
+      </c>
+      <c r="X10" t="s">
         <v>228</v>
       </c>
-      <c r="M10" t="s">
+      <c r="Y10" t="s">
         <v>229</v>
       </c>
-      <c r="O10" t="s">
-        <v>164</v>
-      </c>
-      <c r="P10" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>166</v>
-      </c>
-      <c r="R10" t="s">
-        <v>167</v>
-      </c>
-      <c r="S10" t="s">
-        <v>168</v>
-      </c>
-      <c r="T10" t="s">
-        <v>169</v>
-      </c>
-      <c r="U10" t="s">
-        <v>170</v>
-      </c>
-      <c r="W10" t="s">
-        <v>165</v>
-      </c>
-      <c r="X10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>228</v>
-      </c>
       <c r="Z10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="B11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7132,31 +7160,31 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L11">
-        <v>1.1225374684413019</v>
+        <v>2.0485665253142935</v>
       </c>
       <c r="M11">
-        <v>0.13297302054360291</v>
+        <v>0.2129210940551691</v>
       </c>
       <c r="O11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -7165,16 +7193,16 @@
         <v>21</v>
       </c>
       <c r="T11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="X11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Y11">
         <v>7.5397499999999997</v>
@@ -7185,13 +7213,13 @@
     </row>
     <row r="12" spans="2:26">
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -7200,31 +7228,31 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L12">
-        <v>0.32040150917033461</v>
+        <v>0.27827335220936616</v>
       </c>
       <c r="M12">
-        <v>0.1445289375004486</v>
+        <v>0.1446121970518594</v>
       </c>
       <c r="O12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -7233,16 +7261,16 @@
         <v>21</v>
       </c>
       <c r="T12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="X12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Y12">
         <v>23.645250000000001</v>
@@ -7253,13 +7281,13 @@
     </row>
     <row r="13" spans="2:26">
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -7268,31 +7296,31 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L13">
-        <v>1.1151641595075952</v>
+        <v>6.0169436033943411</v>
       </c>
       <c r="M13">
-        <v>0.18180540825682751</v>
+        <v>0.15175789297489189</v>
       </c>
       <c r="O13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -7301,16 +7329,16 @@
         <v>21</v>
       </c>
       <c r="T13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="X13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y13">
         <v>36.9495</v>
@@ -7321,13 +7349,13 @@
     </row>
     <row r="14" spans="2:26">
       <c r="B14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -7336,31 +7364,31 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L14">
-        <v>0.55837077614555952</v>
+        <v>1.974607487182084</v>
       </c>
       <c r="M14">
-        <v>0.1630535768951481</v>
+        <v>0.17793261062891061</v>
       </c>
       <c r="O14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -7369,16 +7397,16 @@
         <v>21</v>
       </c>
       <c r="T14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="X14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Y14">
         <v>35.276249999999997</v>
@@ -7389,13 +7417,13 @@
     </row>
     <row r="15" spans="2:26">
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -7404,31 +7432,31 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L15">
-        <v>0.4055180903599177</v>
+        <v>3.8785592894875776</v>
       </c>
       <c r="M15">
-        <v>0.1126069245214724</v>
+        <v>0.18655732941430189</v>
       </c>
       <c r="O15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -7437,16 +7465,16 @@
         <v>21</v>
       </c>
       <c r="T15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="X15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y15">
         <v>20.849250000000001</v>
@@ -7457,13 +7485,13 @@
     </row>
     <row r="16" spans="2:26">
       <c r="B16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -7472,31 +7500,31 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L16">
-        <v>2.4551075261477018</v>
+        <v>0.82556800193341606</v>
       </c>
       <c r="M16">
-        <v>0.21584049584095991</v>
+        <v>0.137105895182281</v>
       </c>
       <c r="O16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -7505,16 +7533,16 @@
         <v>21</v>
       </c>
       <c r="T16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="X16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Y16">
         <v>2.3107500000000001</v>
@@ -7525,13 +7553,13 @@
     </row>
     <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7540,31 +7568,31 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L17">
-        <v>2.2141808555519829</v>
+        <v>1.3596128536185663</v>
       </c>
       <c r="M17">
-        <v>0.11537604170683539</v>
+        <v>0.1026366710887449</v>
       </c>
       <c r="O17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -7573,16 +7601,16 @@
         <v>21</v>
       </c>
       <c r="T17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Y17">
         <v>9.8947500000000002</v>
@@ -7593,13 +7621,13 @@
     </row>
     <row r="18" spans="2:26">
       <c r="B18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -7608,31 +7636,31 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L18">
-        <v>3.538246033625021</v>
+        <v>0.4055180903599177</v>
       </c>
       <c r="M18">
-        <v>0.2130812524355743</v>
+        <v>0.1126069246282405</v>
       </c>
       <c r="O18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -7641,16 +7669,16 @@
         <v>21</v>
       </c>
       <c r="T18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W18" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="X18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Y18">
         <v>8.6842500000000005</v>
@@ -7661,13 +7689,13 @@
     </row>
     <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -7676,31 +7704,31 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L19">
-        <v>4.3558806404029173</v>
+        <v>1.0707529779056921</v>
       </c>
       <c r="M19">
-        <v>0.191933579727043</v>
+        <v>0.18141509257551261</v>
       </c>
       <c r="O19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -7709,16 +7737,16 @@
         <v>21</v>
       </c>
       <c r="T19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="X19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Y19">
         <v>29.875499999999999</v>
@@ -7729,13 +7757,13 @@
     </row>
     <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -7744,31 +7772,31 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L20">
-        <v>1.3253694924605515</v>
+        <v>0.55837077614555952</v>
       </c>
       <c r="M20">
-        <v>0.13258881460854249</v>
+        <v>0.16305357809940321</v>
       </c>
       <c r="O20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q20" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -7777,16 +7805,16 @@
         <v>21</v>
       </c>
       <c r="T20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y20">
         <v>40.528500000000001</v>
@@ -7797,13 +7825,13 @@
     </row>
     <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -7812,31 +7840,31 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L21">
-        <v>4.1341545280460359</v>
+        <v>1.1191802126669304</v>
       </c>
       <c r="M21">
-        <v>0.20566396518849861</v>
+        <v>0.12687456604553221</v>
       </c>
       <c r="O21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -7845,16 +7873,16 @@
         <v>21</v>
       </c>
       <c r="T21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Y21">
         <v>3.69225</v>
@@ -7865,13 +7893,13 @@
     </row>
     <row r="22" spans="2:26">
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -7880,31 +7908,31 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L22">
-        <v>2.9308995962428481</v>
+        <v>3.9321545280460359</v>
       </c>
       <c r="M22">
-        <v>0.38075872391230131</v>
+        <v>0.20523004995010369</v>
       </c>
       <c r="O22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P22" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -7913,16 +7941,16 @@
         <v>21</v>
       </c>
       <c r="T22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W22" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X22" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Y22">
         <v>42.84075</v>
@@ -7933,13 +7961,13 @@
     </row>
     <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -7948,31 +7976,31 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K23" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L23">
-        <v>1.7135073625590886</v>
+        <v>1.2747581879814029</v>
       </c>
       <c r="M23">
-        <v>0.26535148650156209</v>
+        <v>0.37647854224061</v>
       </c>
       <c r="O23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q23" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -7981,16 +8009,16 @@
         <v>21</v>
       </c>
       <c r="T23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="X23" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Y23">
         <v>21.626249999999999</v>
@@ -8001,13 +8029,13 @@
     </row>
     <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -8016,31 +8044,31 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L24">
-        <v>0.35013814030741836</v>
+        <v>1.3895551399416923</v>
       </c>
       <c r="M24">
-        <v>0.1380893696842074</v>
+        <v>0.24094492130543529</v>
       </c>
       <c r="O24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P24" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q24" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -8049,33 +8077,33 @@
         <v>21</v>
       </c>
       <c r="T24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W24" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="X24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Y24">
-        <v>29.790749999999999</v>
+        <v>29.77075</v>
       </c>
       <c r="Z24">
-        <v>0.31509985463442491</v>
+        <v>0.31508394092041131</v>
       </c>
     </row>
     <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -8084,31 +8112,31 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L25">
-        <v>2.7555563517396719</v>
+        <v>0.10914657969616609</v>
       </c>
       <c r="M25">
-        <v>0.2403074499135556</v>
+        <v>0.10534484422881241</v>
       </c>
       <c r="O25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P25" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -8117,16 +8145,16 @@
         <v>21</v>
       </c>
       <c r="T25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W25" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="X25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Y25">
         <v>34.175249999999998</v>
@@ -8137,13 +8165,13 @@
     </row>
     <row r="26" spans="2:26">
       <c r="B26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -8152,31 +8180,31 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L26">
-        <v>8.0790956691056017</v>
+        <v>2.2119542216758865</v>
       </c>
       <c r="M26">
-        <v>0.20069291136512271</v>
+        <v>0.22767426821831821</v>
       </c>
       <c r="O26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q26" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -8185,16 +8213,16 @@
         <v>21</v>
       </c>
       <c r="T26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="X26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y26">
         <v>12.687749999999999</v>
@@ -8205,13 +8233,13 @@
     </row>
     <row r="27" spans="2:26">
       <c r="B27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -8220,31 +8248,31 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L27">
-        <v>4.6685340400007895</v>
+        <v>7.9247611034863779</v>
       </c>
       <c r="M27">
-        <v>0.16876456670337081</v>
+        <v>0.1998419250349755</v>
       </c>
       <c r="O27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P27" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -8253,16 +8281,16 @@
         <v>21</v>
       </c>
       <c r="T27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W27" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="X27" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Y27">
         <v>12.513</v>
@@ -8273,13 +8301,13 @@
     </row>
     <row r="28" spans="2:26">
       <c r="B28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -8288,31 +8316,31 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K28" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L28">
-        <v>2.1854625110478083</v>
+        <v>4.3955340400007898</v>
       </c>
       <c r="M28">
-        <v>0.25045214590175979</v>
+        <v>0.16623078709058009</v>
       </c>
       <c r="O28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q28" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -8321,16 +8349,16 @@
         <v>21</v>
       </c>
       <c r="T28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="W28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="X28" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Y28">
         <v>38.378999999999998</v>
@@ -8341,13 +8369,13 @@
     </row>
     <row r="29" spans="2:26">
       <c r="B29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -8356,33 +8384,33 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L29">
-        <v>5.225486475009669</v>
+        <v>0.5780310412144154</v>
       </c>
       <c r="M29">
-        <v>0.15580057581145881</v>
+        <v>0.1462599435614502</v>
       </c>
     </row>
     <row r="30" spans="2:26">
       <c r="B30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -8391,33 +8419,33 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L30">
-        <v>0.47845858029330623</v>
+        <v>0.33899815049521981</v>
       </c>
       <c r="M30">
-        <v>0.27069559137047811</v>
+        <v>0.23662570987936671</v>
       </c>
     </row>
     <row r="31" spans="2:26">
       <c r="B31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -8426,33 +8454,33 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L31">
-        <v>1.4932376772991292</v>
+        <v>1.0010891133233775</v>
       </c>
       <c r="M31">
-        <v>0.28680072771864068</v>
+        <v>0.1583153713439035</v>
       </c>
     </row>
     <row r="32" spans="2:26">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -8461,33 +8489,33 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K32" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L32">
-        <v>1.1142643402792876</v>
+        <v>0.1594390600826095</v>
       </c>
       <c r="M32">
-        <v>0.1636259514075715</v>
+        <v>0.2426519727704734</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -8496,33 +8524,33 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L33">
-        <v>2.1629055032192892</v>
+        <v>0.5482230079548871</v>
       </c>
       <c r="M33">
-        <v>0.28139772056705548</v>
+        <v>0.20730326722169851</v>
       </c>
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -8531,33 +8559,33 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L34">
         <v>1.4643486628297562</v>
       </c>
       <c r="M34">
-        <v>0.1977549054771833</v>
+        <v>0.19775490648008989</v>
       </c>
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D35" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -8566,22 +8594,22 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J35" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L35">
         <v>1.2331970370370371</v>
       </c>
       <c r="M35">
-        <v>8.1107030231653096E-2</v>
+        <v>8.1107030707579603E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8590,27 +8618,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{796A1720-BB4D-4210-B3DC-FDB684EB262B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D052B9A5-D8E5-4D6C-838E-59F9C7DECDA3}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E10">
         <v>2023</v>
@@ -8625,30 +8653,30 @@
         <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -8669,10 +8697,10 @@
         <v>146</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -8681,15 +8709,15 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -8707,13 +8735,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -8722,15 +8750,15 @@
         <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -8748,13 +8776,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -8763,15 +8791,15 @@
         <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -8789,13 +8817,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -8804,15 +8832,15 @@
         <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -8830,13 +8858,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -8845,15 +8873,15 @@
         <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P15" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -8874,10 +8902,10 @@
         <v>146</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -8886,15 +8914,15 @@
         <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -8912,13 +8940,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -8927,15 +8955,15 @@
         <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -8953,13 +8981,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -8968,15 +8996,15 @@
         <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -8994,13 +9022,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -9009,15 +9037,15 @@
         <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -9035,13 +9063,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -9050,15 +9078,15 @@
         <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P20" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -9079,10 +9107,10 @@
         <v>146</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -9091,15 +9119,15 @@
         <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P21" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -9117,13 +9145,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -9132,15 +9160,15 @@
         <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P22" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -9158,13 +9186,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -9173,15 +9201,15 @@
         <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P23" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -9202,10 +9230,10 @@
         <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -9214,15 +9242,15 @@
         <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P24" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -9240,13 +9268,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -9255,15 +9283,15 @@
         <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P25" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -9281,13 +9309,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -9296,15 +9324,15 @@
         <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -9325,10 +9353,10 @@
         <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -9337,15 +9365,15 @@
         <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P27" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -9363,12 +9391,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -9386,12 +9414,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -9414,7 +9442,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -9432,12 +9460,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -9455,12 +9483,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -9483,7 +9511,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -9501,12 +9529,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -9524,12 +9552,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -9547,12 +9575,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -9570,12 +9598,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -9598,7 +9626,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -9616,12 +9644,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -9639,12 +9667,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -9667,7 +9695,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -9685,12 +9713,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -9708,12 +9736,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -9736,7 +9764,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -9754,12 +9782,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -9777,12 +9805,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -9805,7 +9833,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -9823,12 +9851,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -9846,12 +9874,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -9874,7 +9902,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -9892,12 +9920,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -9915,12 +9943,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -9938,12 +9966,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -9961,12 +9989,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -9989,7 +10017,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -10007,12 +10035,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -10030,12 +10058,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -10058,7 +10086,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -10076,12 +10104,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -10099,12 +10127,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -10127,7 +10155,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -10145,12 +10173,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -10168,15 +10196,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C64" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -10196,10 +10224,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C65" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -10214,15 +10242,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C66" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -10237,15 +10265,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C67" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -10260,15 +10288,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C68" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -10283,15 +10311,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
+        <v>408</v>
+      </c>
+      <c r="C69" t="s">
         <v>407</v>
-      </c>
-      <c r="C69" t="s">
-        <v>406</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -10311,10 +10339,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
+        <v>408</v>
+      </c>
+      <c r="C70" t="s">
         <v>407</v>
-      </c>
-      <c r="C70" t="s">
-        <v>406</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -10329,15 +10357,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
+        <v>408</v>
+      </c>
+      <c r="C71" t="s">
         <v>407</v>
-      </c>
-      <c r="C71" t="s">
-        <v>406</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -10352,15 +10380,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
+        <v>408</v>
+      </c>
+      <c r="C72" t="s">
         <v>407</v>
-      </c>
-      <c r="C72" t="s">
-        <v>406</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -10375,15 +10403,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
+        <v>408</v>
+      </c>
+      <c r="C73" t="s">
         <v>407</v>
-      </c>
-      <c r="C73" t="s">
-        <v>406</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -10398,7 +10426,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
